--- a/docs/output/本月對帳差額與應收餘額表_202610.xlsx
+++ b/docs/output/本月對帳差額與應收餘額表_202610.xlsx
@@ -10,6 +10,7 @@
     <sheet name="對帳差額總表" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="玉山單筆沖銷對照" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="門市現金雙層審核與異常" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="平台手續費發票缺漏追蹤" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -583,7 +584,7 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="19.5" customWidth="1" min="7" max="7"/>
-    <col width="51" customWidth="1" min="8" max="8"/>
+    <col width="67.5" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -645,7 +646,7 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>180718</v>
+        <v>186446</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>167270</v>
@@ -654,11 +655,11 @@
         <v>0</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>13448</v>
+        <v>19176</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>⏳ 門市尚有 $13,448 現金待存入銀行</t>
+          <t>⏳ 門市尚有 $19,176 現金待存入銀行</t>
         </is>
       </c>
     </row>
@@ -679,7 +680,7 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>254619</v>
+        <v>261117</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>228573</v>
@@ -688,11 +689,11 @@
         <v>0</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>26046</v>
+        <v>32544</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>⏳ 連加網路正常撥款作業中（約待撥 $26,046）</t>
+          <t>⏳ 連加網路撥款中（預估手續費 $752 / 實撥淨額 $31,792）</t>
         </is>
       </c>
     </row>
@@ -713,7 +714,7 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>50903</v>
+        <v>52523</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>28996</v>
@@ -722,11 +723,11 @@
         <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>21907</v>
+        <v>23527</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>⏳ Uber Eats 外送週期結算撥款中（約待撥 $21,907）</t>
+          <t>⏳ Uber Eats 結算中（預估抽成發票 $17,333 / 待撥淨額 $6,194）</t>
         </is>
       </c>
     </row>
@@ -747,7 +748,7 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1580</v>
+        <v>3970</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>1870</v>
@@ -756,11 +757,11 @@
         <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-290</v>
+        <v>2100</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>✅ 已全數結清沖銷</t>
+          <t>結算中（待撥 $2,100）</t>
         </is>
       </c>
     </row>
@@ -828,7 +829,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>⏳ 連加網路正常撥款作業中（約待撥 $75,090）</t>
+          <t>⏳ 連加網路撥款中（預估手續費 $1,735 / 實撥淨額 $73,355）</t>
         </is>
       </c>
     </row>
@@ -862,7 +863,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>⏳ Uber Eats 外送週期結算撥款中（約待撥 $11,032）</t>
+          <t>⏳ Uber Eats 結算中（預估抽成發票 $5,390 / 待撥淨額 $5,642）</t>
         </is>
       </c>
     </row>
@@ -896,7 +897,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>⏳ Foodpanda 外送週期結算撥款中（約待撥 $15,596）</t>
+          <t>⏳ Foodpanda 結算中（預估抽成發票 $5,240 / 待撥淨額 $10,356）</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3270,10 +3271,11 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="79.5" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="22.5" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="106.5" customWidth="1" min="9" max="9"/>
+    <col width="40.5" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="22.5" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="157.5" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3304,20 +3306,25 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>短溢差額 (實存-應收)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>第二層：玉山銀行入帳狀態</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>雙層審核結論</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>已延遲天數</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>處置建議</t>
         </is>
@@ -3347,20 +3354,25 @@
       </c>
       <c r="F2" s="10" t="inlineStr">
         <is>
+          <t>✓ 金額相符</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
           <t>⏳ 存摺尚未到帳/未更新</t>
         </is>
       </c>
-      <c r="G2" s="19" t="inlineStr">
+      <c r="H2" s="19" t="inlineStr">
         <is>
           <t>🟡 門市已申報 (待銀行入帳)</t>
         </is>
       </c>
-      <c r="H2" s="10" t="inlineStr">
+      <c r="I2" s="10" t="inlineStr">
         <is>
           <t>8 天</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>總表已登記提存，待存摺更新自動結清 (申報於 2026/10/16 存入 $31,720 (2026-10-14~2026-10-15累計))</t>
         </is>
@@ -3390,20 +3402,25 @@
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
+          <t>✓ 金額相符</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
           <t>⏳ 存摺尚未到帳/未更新</t>
         </is>
       </c>
-      <c r="G3" s="19" t="inlineStr">
+      <c r="H3" s="19" t="inlineStr">
         <is>
           <t>🟡 門市已申報 (待銀行入帳)</t>
         </is>
       </c>
-      <c r="H3" s="10" t="inlineStr">
+      <c r="I3" s="10" t="inlineStr">
         <is>
           <t>7 天</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>總表已登記提存，待存摺更新自動結清 (申報於 2026/10/16 存入 $31,720 (2026-10-14~2026-10-15累計))</t>
         </is>
@@ -3433,20 +3450,25 @@
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
+          <t>✓ 金額相符</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
           <t>⏳ 存摺尚未到帳/未更新</t>
         </is>
       </c>
-      <c r="G4" s="19" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>🟡 門市已申報 (待銀行入帳)</t>
         </is>
       </c>
-      <c r="H4" s="10" t="inlineStr">
+      <c r="I4" s="10" t="inlineStr">
         <is>
           <t>6 天</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>總表已登記提存，待存摺更新自動結清 (申報於 2026/10/19 存入 $44,659 (2026-10-16~2026-10-18累計))</t>
         </is>
@@ -3476,20 +3498,25 @@
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
+          <t>✓ 金額相符</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
           <t>⏳ 存摺尚未到帳/未更新</t>
         </is>
       </c>
-      <c r="G5" s="19" t="inlineStr">
+      <c r="H5" s="19" t="inlineStr">
         <is>
           <t>🟡 門市已申報 (待銀行入帳)</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="I5" s="10" t="inlineStr">
         <is>
           <t>5 天</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>總表已登記提存，待存摺更新自動結清 (申報於 2026/10/19 存入 $44,659 (2026-10-16~2026-10-18累計))</t>
         </is>
@@ -3519,20 +3546,25 @@
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
+          <t>✓ 金額相符</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
           <t>⏳ 存摺尚未到帳/未更新</t>
         </is>
       </c>
-      <c r="G6" s="19" t="inlineStr">
+      <c r="H6" s="19" t="inlineStr">
         <is>
           <t>🟡 門市已申報 (待銀行入帳)</t>
         </is>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="I6" s="10" t="inlineStr">
         <is>
           <t>4 天</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>總表已登記提存，待存摺更新自動結清 (申報於 2026/10/19 存入 $44,659 (2026-10-16~2026-10-18累計))</t>
         </is>
@@ -3562,22 +3594,27 @@
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
+          <t>⚠️ 短少 -$1,020 (應收合 $25,990)</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
           <t>⏳ 存摺尚未到帳/未更新</t>
         </is>
       </c>
-      <c r="G7" s="19" t="inlineStr">
+      <c r="H7" s="19" t="inlineStr">
         <is>
           <t>🟡 門市已申報 (待銀行入帳)</t>
         </is>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="I7" s="10" t="inlineStr">
         <is>
           <t>3 天</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>總表已登記提存，待存摺更新自動結清 (申報於 2026/10/21 存入 $24,970 (2026-10-19~2026-10-20累計))</t>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>【注意短溢：⚠️ 短少 -$1,020 (應收合 $25,990)】總表已登記提存，待存摺更新自動結清 (申報於 2026/10/21 存入 $24,970 (2026-10-19~2026-10-20累計))</t>
         </is>
       </c>
     </row>
@@ -3605,20 +3642,25 @@
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
+          <t>⏳ 待存入</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
           <t>❌ 存摺未見入帳</t>
         </is>
       </c>
-      <c r="G8" s="20" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>🔴 門市未存 (留店未存)</t>
         </is>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr">
         <is>
           <t>2 天</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>門市正常交班處理中，待總表申報或存款</t>
         </is>
@@ -3648,22 +3690,27 @@
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
+          <t>⚠️ 短少 -$1,020 (應收合 $25,990)</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
           <t>⏳ 存摺尚未到帳/未更新</t>
         </is>
       </c>
-      <c r="G9" s="19" t="inlineStr">
+      <c r="H9" s="19" t="inlineStr">
         <is>
           <t>🟡 門市已申報 (待銀行入帳)</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t>2 天</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>總表已登記提存，待存摺更新自動結清 (申報於 2026/10/21 存入 $24,970 (2026-10-19~2026-10-20累計))</t>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>【注意短溢：⚠️ 短少 -$1,020 (應收合 $25,990)】總表已登記提存，待存摺更新自動結清 (申報於 2026/10/21 存入 $24,970 (2026-10-19~2026-10-20累計))</t>
         </is>
       </c>
     </row>
@@ -3691,20 +3738,25 @@
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
+          <t>⏳ 待存入</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
           <t>❌ 存摺未見入帳</t>
         </is>
       </c>
-      <c r="G10" s="20" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>🔴 門市未存 (留店未存)</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>1 天</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>門市正常交班處理中，待總表申報或存款</t>
         </is>
@@ -3734,22 +3786,373 @@
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
+          <t>⏳ 待存入</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
           <t>❌ 存摺未見入帳</t>
         </is>
       </c>
-      <c r="G11" s="20" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>🔴 門市未存 (留店未存)</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="I11" s="10" t="inlineStr">
         <is>
           <t>1 天</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>門市正常交班處理中，待總表申報或存款</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>月宮 (月下餐飲)</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>5728</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>❌ 總表U欄空白未填</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>⏳ 待存入</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>❌ 存摺未見入帳</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>🔴 門市未存 (留店未存)</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>0 天</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>門市正常交班處理中，待總表申報或存款</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16.5" customWidth="1" min="6" max="6"/>
+    <col width="19.5" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="22.5" customWidth="1" min="9" max="9"/>
+    <col width="75" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>事業體</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>平台名稱</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>廠商統編</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>抽成/手續費率</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>本月 POS 營收</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>預估全月手續費含稅總額</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>預估可扣抵 5% 進項稅額</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>已匯入發票沖銷</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>目前發票追蹤狀態</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>會計核對與索取建議</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>月宮 (月下餐飲)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LINE Pay (連加網路)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>99024139</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2.31%</t>
+        </is>
+      </c>
+      <c r="E2" s="12" t="n">
+        <v>261117</v>
+      </c>
+      <c r="F2" s="12" t="n">
+        <v>3319</v>
+      </c>
+      <c r="G2" s="12" t="n">
+        <v>158</v>
+      </c>
+      <c r="H2" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>🟡 傳票已提列・待核對月底發票</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>月底核對連加網路 (99024139) 電子發票約 $3,319（含可扣抵進項稅額 $158）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>月宮 (月下餐飲)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Uber Eats (優步科技)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>83118125</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>約 33%</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="n">
+        <v>52523</v>
+      </c>
+      <c r="F3" s="12" t="n">
+        <v>17333</v>
+      </c>
+      <c r="G3" s="12" t="n">
+        <v>825</v>
+      </c>
+      <c r="H3" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>🔴 待取得發票沖銷差額</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>請下載優步 (83118125) 手續費發票約 $17,333 沖銷應收差額（可扣抵稅額 $825）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LINE Pay (連加網路)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>99024139</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2.31%</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="n">
+        <v>170122</v>
+      </c>
+      <c r="F4" s="12" t="n">
+        <v>2777</v>
+      </c>
+      <c r="G4" s="12" t="n">
+        <v>132</v>
+      </c>
+      <c r="H4" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>🟡 傳票已提列・待核對月底發票</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>月底核對連加網路 (99024139) 電子發票約 $2,777（含可扣抵進項稅額 $132）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Uber Eats (優步科技)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>83118125</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>約 33%</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>16333</v>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>5390</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>257</v>
+      </c>
+      <c r="H5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>🔴 待取得發票沖銷差額</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>請下載優步 (83118125) 手續費發票約 $5,390 沖銷應收差額（可扣抵稅額 $257）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Foodpanda (富胖達)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>53075607</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>約 33.6%</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>15596</v>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>5240</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>250</v>
+      </c>
+      <c r="H6" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>🔴 待取得發票沖銷差額</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>請下載富胖達 (53075607) 手續費發票約 $5,240 沖銷應收差額（可扣抵稅額 $250）</t>
         </is>
       </c>
     </row>

--- a/docs/output/本月對帳差額與應收餘額表_202610.xlsx
+++ b/docs/output/本月對帳差額與應收餘額表_202610.xlsx
@@ -580,11 +580,11 @@
     <col width="37.5" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="13.5" customWidth="1" min="3" max="3"/>
-    <col width="22.5" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="19.5" customWidth="1" min="7" max="7"/>
-    <col width="67.5" customWidth="1" min="8" max="8"/>
+    <col width="13.5" customWidth="1" min="4" max="4"/>
+    <col width="22.5" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="25.5" customWidth="1" min="7" max="7"/>
+    <col width="73.5" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -605,22 +605,22 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>POS 累計營收 (本月權責)</t>
+          <t>① POS 原始額</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>所屬本月實收沖銷</t>
+          <t>② 扣手續費後實收額 (實收)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>手續費發票已沖</t>
+          <t>③ 玉山銀行已存額 (已存)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>目前未收差額 (真實誤差)</t>
+          <t>④ 推算未入帳差額 (實收-已存)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -649,17 +649,17 @@
         <v>186446</v>
       </c>
       <c r="E2" s="3" t="n">
+        <v>186446</v>
+      </c>
+      <c r="F2" s="3" t="n">
         <v>167270</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>19176</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>⏳ 門市尚有 $19,176 現金待存入銀行</t>
+          <t>⏳ 實收現金 $186,446 / 已存現金 $167,270 ➔ 待入帳 $19,176</t>
         </is>
       </c>
     </row>
@@ -683,17 +683,17 @@
         <v>261117</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>228573</v>
+        <v>255075</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0</v>
+        <v>226298</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>32544</v>
+        <v>28777</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>⏳ 連加網路撥款中（預估手續費 $752 / 實撥淨額 $31,792）</t>
+          <t>⏳ 實收LINE Pay $255,075 / 已存 $226,298 ➔ 待入帳 $28,777</t>
         </is>
       </c>
     </row>
@@ -717,17 +717,17 @@
         <v>52523</v>
       </c>
       <c r="E4" s="3" t="n">
+        <v>35190</v>
+      </c>
+      <c r="F4" s="3" t="n">
         <v>28996</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G4" s="3" t="n">
-        <v>23527</v>
+        <v>6194</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>⏳ Uber Eats 結算中（預估抽成發票 $17,333 / 待撥淨額 $6,194）</t>
+          <t>⏳ 實收Uber Eats $35,190 / 已存 $28,996 ➔ 待入帳 $6,194</t>
         </is>
       </c>
     </row>
@@ -751,10 +751,10 @@
         <v>3970</v>
       </c>
       <c r="E5" s="3" t="n">
+        <v>3970</v>
+      </c>
+      <c r="F5" s="3" t="n">
         <v>1870</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>2100</v>
@@ -782,20 +782,20 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>322417</v>
+        <v>336307</v>
       </c>
       <c r="E6" s="3" t="n">
+        <v>336307</v>
+      </c>
+      <c r="F6" s="3" t="n">
         <v>209228</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G6" s="3" t="n">
-        <v>113189</v>
+        <v>127079</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>⏳ 門市尚有 $113,189 現金待存入銀行</t>
+          <t>⏳ 實收現金 $336,307 / 已存現金 $209,228 ➔ 待入帳 $127,079</t>
         </is>
       </c>
     </row>
@@ -816,20 +816,20 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>170122</v>
+        <v>176092</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>95032</v>
+        <v>172017</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0</v>
+        <v>93990</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>75090</v>
+        <v>78027</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>⏳ 連加網路撥款中（預估手續費 $1,735 / 實撥淨額 $73,355）</t>
+          <t>⏳ 實收LINE Pay $172,017 / 已存 $93,990 ➔ 待入帳 $78,027</t>
         </is>
       </c>
     </row>
@@ -853,17 +853,17 @@
         <v>16333</v>
       </c>
       <c r="E8" s="3" t="n">
+        <v>11265</v>
+      </c>
+      <c r="F8" s="3" t="n">
         <v>5301</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G8" s="3" t="n">
-        <v>11032</v>
+        <v>5964</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>⏳ Uber Eats 結算中（預估抽成發票 $5,390 / 待撥淨額 $5,642）</t>
+          <t>⏳ 實收Uber Eats $11,265 / 已存 $5,301 ➔ 待入帳 $5,964</t>
         </is>
       </c>
     </row>
@@ -884,20 +884,20 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>15596</v>
+        <v>15930</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>10578</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>15596</v>
+        <v>10578</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>⏳ Foodpanda 結算中（預估抽成發票 $5,240 / 待撥淨額 $10,356）</t>
+          <t>⏳ 實收Foodpanda $10,578 / 已存 $0 ➔ 待入帳 $10,578</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3853,6 +3853,54 @@
         </is>
       </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>門市正常交班處理中，待總表申報或存款</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>13890</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>❌ 總表U欄空白未填</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>⏳ 待存入</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>❌ 存摺未見入帳</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>🔴 門市未存 (留店未存)</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>0 天</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>門市正常交班處理中，待總表申報或存款</t>
         </is>
@@ -3961,10 +4009,10 @@
         <v>261117</v>
       </c>
       <c r="F2" s="12" t="n">
-        <v>3319</v>
+        <v>6042</v>
       </c>
       <c r="G2" s="12" t="n">
-        <v>158</v>
+        <v>288</v>
       </c>
       <c r="H2" s="12" t="n">
         <v>0</v>
@@ -3976,7 +4024,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>月底核對連加網路 (99024139) 電子發票約 $3,319（含可扣抵進項稅額 $158）</t>
+          <t>月底核對連加網路 (99024139) 電子發票約 $6,042（含可扣抵進項稅額 $288）</t>
         </is>
       </c>
     </row>
@@ -4046,13 +4094,13 @@
         </is>
       </c>
       <c r="E4" s="12" t="n">
-        <v>170122</v>
+        <v>176092</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>2777</v>
+        <v>4075</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>132</v>
+        <v>194</v>
       </c>
       <c r="H4" s="12" t="n">
         <v>0</v>
@@ -4064,7 +4112,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>月底核對連加網路 (99024139) 電子發票約 $2,777（含可扣抵進項稅額 $132）</t>
+          <t>月底核對連加網路 (99024139) 電子發票約 $4,075（含可扣抵進項稅額 $194）</t>
         </is>
       </c>
     </row>
@@ -4086,17 +4134,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>約 33%</t>
+          <t>約 31~33%</t>
         </is>
       </c>
       <c r="E5" s="12" t="n">
         <v>16333</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>5390</v>
+        <v>5068</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>257</v>
+        <v>241</v>
       </c>
       <c r="H5" s="12" t="n">
         <v>0</v>
@@ -4108,7 +4156,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>請下載優步 (83118125) 手續費發票約 $5,390 沖銷應收差額（可扣抵稅額 $257）</t>
+          <t>請下載優步 (83118125) 手續費發票約 $5,068 沖銷應收差額（可扣抵稅額 $241）</t>
         </is>
       </c>
     </row>
@@ -4134,13 +4182,13 @@
         </is>
       </c>
       <c r="E6" s="12" t="n">
-        <v>15596</v>
+        <v>15930</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>5240</v>
+        <v>5352</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="H6" s="12" t="n">
         <v>0</v>
@@ -4152,7 +4200,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>請下載富胖達 (53075607) 手續費發票約 $5,240 沖銷應收差額（可扣抵稅額 $250）</t>
+          <t>請下載富胖達 (53075607) 手續費發票約 $5,352 沖銷應收差額（可扣抵稅額 $255）</t>
         </is>
       </c>
     </row>

--- a/docs/output/本月對帳差額與應收餘額表_202610.xlsx
+++ b/docs/output/本月對帳差額與應收餘額表_202610.xlsx
@@ -3929,7 +3929,7 @@
     <col width="19.5" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="22.5" customWidth="1" min="9" max="9"/>
-    <col width="75" customWidth="1" min="10" max="10"/>
+    <col width="64.5" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>月底核對連加網路 (99024139) 電子發票約 $6,042（含可扣抵進項稅額 $288）</t>
+          <t>連加網路 (99024139) 手續費約 $6,042（含可扣抵進項稅額 $288）</t>
         </is>
       </c>
     </row>
@@ -4068,7 +4068,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>請下載優步 (83118125) 手續費發票約 $17,333 沖銷應收差額（可扣抵稅額 $825）</t>
+          <t>優步科技 (83118125) 手續費發票約 $17,333（含可扣抵稅額 $825）</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4112,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>月底核對連加網路 (99024139) 電子發票約 $4,075（含可扣抵進項稅額 $194）</t>
+          <t>連加網路 (99024139) 手續費約 $4,075（含可扣抵進項稅額 $194）</t>
         </is>
       </c>
     </row>
@@ -4156,7 +4156,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>請下載優步 (83118125) 手續費發票約 $5,068 沖銷應收差額（可扣抵稅額 $241）</t>
+          <t>優步科技 (83118125) 手續費發票約 $5,068（含可扣抵稅額 $241）</t>
         </is>
       </c>
     </row>
@@ -4200,7 +4200,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>請下載富胖達 (53075607) 手續費發票約 $5,352 沖銷應收差額（可扣抵稅額 $255）</t>
+          <t>富胖達 (53075607) 手續費發票約 $5,352（含可扣抵稅額 $255）</t>
         </is>
       </c>
     </row>

--- a/docs/output/本月對帳差額與應收餘額表_202610.xlsx
+++ b/docs/output/本月對帳差額與應收餘額表_202610.xlsx
@@ -646,20 +646,20 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>186446</v>
+        <v>203500</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>186446</v>
+        <v>203500</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>167270</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>19176</v>
+        <v>36230</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>⏳ 實收現金 $186,446 / 已存現金 $167,270 ➔ 待入帳 $19,176</t>
+          <t>⏳ 實收現金 $203,500 / 已存現金 $167,270 ➔ 待入帳 $36,230</t>
         </is>
       </c>
     </row>
@@ -680,20 +680,20 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>261117</v>
+        <v>295484</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>255075</v>
+        <v>288646</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>226298</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>28777</v>
+        <v>62348</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>⏳ 實收LINE Pay $255,075 / 已存 $226,298 ➔ 待入帳 $28,777</t>
+          <t>⏳ 實收LINE Pay $288,646 / 已存 $226,298 ➔ 待入帳 $62,348</t>
         </is>
       </c>
     </row>
@@ -714,20 +714,20 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>52523</v>
+        <v>60856</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>35190</v>
+        <v>40774</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>28996</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>6194</v>
+        <v>11778</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>⏳ 實收Uber Eats $35,190 / 已存 $28,996 ➔ 待入帳 $6,194</t>
+          <t>⏳ 實收Uber Eats $40,774 / 已存 $28,996 ➔ 待入帳 $11,778</t>
         </is>
       </c>
     </row>
@@ -782,20 +782,20 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>336307</v>
+        <v>369237</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>336307</v>
+        <v>369237</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>209228</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>127079</v>
+        <v>160009</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>⏳ 實收現金 $336,307 / 已存現金 $209,228 ➔ 待入帳 $127,079</t>
+          <t>⏳ 實收現金 $369,237 / 已存現金 $209,228 ➔ 待入帳 $160,009</t>
         </is>
       </c>
     </row>
@@ -816,20 +816,20 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>176092</v>
+        <v>187672</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>172017</v>
+        <v>183329</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>93990</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>78027</v>
+        <v>89339</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>⏳ 實收LINE Pay $172,017 / 已存 $93,990 ➔ 待入帳 $78,027</t>
+          <t>⏳ 實收LINE Pay $183,329 / 已存 $93,990 ➔ 待入帳 $89,339</t>
         </is>
       </c>
     </row>
@@ -850,20 +850,20 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>16333</v>
+        <v>17385</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>11265</v>
+        <v>11990</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>5301</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>5964</v>
+        <v>6689</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>⏳ 實收Uber Eats $11,265 / 已存 $5,301 ➔ 待入帳 $5,964</t>
+          <t>⏳ 實收Uber Eats $11,990 / 已存 $5,301 ➔ 待入帳 $6,689</t>
         </is>
       </c>
     </row>
@@ -884,20 +884,20 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>15930</v>
+        <v>18722</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>10578</v>
+        <v>12431</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>10578</v>
+        <v>12431</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>⏳ 實收Foodpanda $10,578 / 已存 $0 ➔ 待入帳 $10,578</t>
+          <t>⏳ 實收Foodpanda $12,431 / 已存 $0 ➔ 待入帳 $12,431</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3864,43 +3864,283 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>月宮 (月下餐飲)</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>1935</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>❌ 總表U欄空白未填</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>⏳ 待存入</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>❌ 存摺未見入帳</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>🔴 門市未存 (留店未存)</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>0 天</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>門市正常交班處理中，待總表申報或存款</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>月宮 (月下餐飲)</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="n">
+        <v>9876</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>❌ 總表U欄空白未填</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>⏳ 待存入</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>❌ 存摺未見入帳</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>🔴 門市未存 (留店未存)</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>0 天</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>門市正常交班處理中，待總表申報或存款</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>月宮 (月下餐飲)</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>5243</v>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>❌ 總表U欄空白未填</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>⏳ 待存入</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>❌ 存摺未見入帳</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>🔴 門市未存 (留店未存)</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>0 天</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>門市正常交班處理中，待總表申報或存款</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>隨意小吃</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="D16" s="12" t="n">
         <v>13890</v>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>❌ 總表U欄空白未填</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F16" s="10" t="inlineStr">
         <is>
           <t>⏳ 待存入</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>❌ 存摺未見入帳</t>
         </is>
       </c>
-      <c r="H13" s="20" t="inlineStr">
+      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>🔴 門市未存 (留店未存)</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr">
+      <c r="I16" s="10" t="inlineStr">
         <is>
           <t>0 天</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>門市正常交班處理中，待總表申報或存款</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>18100</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>❌ 總表U欄空白未填</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>⏳ 待存入</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>❌ 存摺未見入帳</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>🔴 門市未存 (留店未存)</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>0 天</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>門市正常交班處理中，待總表申報或存款</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>14830</v>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>❌ 總表U欄空白未填</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>⏳ 待存入</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>❌ 存摺未見入帳</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>🔴 門市未存 (留店未存)</t>
+        </is>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>0 天</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>門市正常交班處理中，待總表申報或存款</t>
         </is>
@@ -4006,13 +4246,13 @@
         </is>
       </c>
       <c r="E2" s="12" t="n">
-        <v>261117</v>
+        <v>295484</v>
       </c>
       <c r="F2" s="12" t="n">
-        <v>6042</v>
+        <v>6838</v>
       </c>
       <c r="G2" s="12" t="n">
-        <v>288</v>
+        <v>326</v>
       </c>
       <c r="H2" s="12" t="n">
         <v>0</v>
@@ -4024,7 +4264,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>連加網路 (99024139) 手續費約 $6,042（含可扣抵進項稅額 $288）</t>
+          <t>連加網路 (99024139) 手續費約 $6,838（含可扣抵進項稅額 $326）</t>
         </is>
       </c>
     </row>
@@ -4050,13 +4290,13 @@
         </is>
       </c>
       <c r="E3" s="12" t="n">
-        <v>52523</v>
+        <v>60856</v>
       </c>
       <c r="F3" s="12" t="n">
-        <v>17333</v>
+        <v>20082</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>825</v>
+        <v>956</v>
       </c>
       <c r="H3" s="12" t="n">
         <v>0</v>
@@ -4068,7 +4308,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>優步科技 (83118125) 手續費發票約 $17,333（含可扣抵稅額 $825）</t>
+          <t>優步科技 (83118125) 手續費發票約 $20,082（含可扣抵稅額 $956）</t>
         </is>
       </c>
     </row>
@@ -4094,13 +4334,13 @@
         </is>
       </c>
       <c r="E4" s="12" t="n">
-        <v>176092</v>
+        <v>187672</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>4075</v>
+        <v>4343</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="H4" s="12" t="n">
         <v>0</v>
@@ -4112,7 +4352,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>連加網路 (99024139) 手續費約 $4,075（含可扣抵進項稅額 $194）</t>
+          <t>連加網路 (99024139) 手續費約 $4,343（含可扣抵進項稅額 $207）</t>
         </is>
       </c>
     </row>
@@ -4138,13 +4378,13 @@
         </is>
       </c>
       <c r="E5" s="12" t="n">
-        <v>16333</v>
+        <v>17385</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>5068</v>
+        <v>5395</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="H5" s="12" t="n">
         <v>0</v>
@@ -4156,7 +4396,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>優步科技 (83118125) 手續費發票約 $5,068（含可扣抵稅額 $241）</t>
+          <t>優步科技 (83118125) 手續費發票約 $5,395（含可扣抵稅額 $257）</t>
         </is>
       </c>
     </row>
@@ -4182,13 +4422,13 @@
         </is>
       </c>
       <c r="E6" s="12" t="n">
-        <v>15930</v>
+        <v>18722</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>5352</v>
+        <v>6291</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>255</v>
+        <v>300</v>
       </c>
       <c r="H6" s="12" t="n">
         <v>0</v>
@@ -4200,7 +4440,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>富胖達 (53075607) 手續費發票約 $5,352（含可扣抵稅額 $255）</t>
+          <t>富胖達 (53075607) 手續費發票約 $6,291（含可扣抵稅額 $300）</t>
         </is>
       </c>
     </row>

--- a/docs/output/本月對帳差額與應收餘額表_202610.xlsx
+++ b/docs/output/本月對帳差額與應收餘額表_202610.xlsx
@@ -3733,22 +3733,22 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>❌ 總表U欄空白未填</t>
+          <t>✅ 申報於 2026/10/27 存入 $25,361 (2026-10-21~2026-10-25累計)</t>
         </is>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>⏳ 待存入</t>
+          <t>➕ 溢存 +$845 (應收合 $24,516)</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>❌ 存摺未見入帳</t>
-        </is>
-      </c>
-      <c r="H10" s="20" t="inlineStr">
-        <is>
-          <t>🔴 門市未存 (留店未存)</t>
+          <t>⏳ 存摺尚未到帳/未更新</t>
+        </is>
+      </c>
+      <c r="H10" s="19" t="inlineStr">
+        <is>
+          <t>🟡 門市已申報 (待銀行入帳)</t>
         </is>
       </c>
       <c r="I10" s="10" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>門市正常交班處理中，待總表申報或存款</t>
+          <t>【注意短溢：➕ 溢存 +$845 (應收合 $24,516)】總表已登記提存，待存摺更新自動結清 (申報於 2026/10/27 存入 $25,361 (2026-10-21~2026-10-25累計))</t>
         </is>
       </c>
     </row>
@@ -3829,22 +3829,22 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>❌ 總表U欄空白未填</t>
+          <t>✅ 申報於 2026/10/27 存入 $25,361 (2026-10-21~2026-10-25累計)</t>
         </is>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>⏳ 待存入</t>
+          <t>➕ 溢存 +$845 (應收合 $24,516)</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>❌ 存摺未見入帳</t>
-        </is>
-      </c>
-      <c r="H12" s="20" t="inlineStr">
-        <is>
-          <t>🔴 門市未存 (留店未存)</t>
+          <t>⏳ 存摺尚未到帳/未更新</t>
+        </is>
+      </c>
+      <c r="H12" s="19" t="inlineStr">
+        <is>
+          <t>🟡 門市已申報 (待銀行入帳)</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>門市正常交班處理中，待總表申報或存款</t>
+          <t>【注意短溢：➕ 溢存 +$845 (應收合 $24,516)】總表已登記提存，待存摺更新自動結清 (申報於 2026/10/27 存入 $25,361 (2026-10-21~2026-10-25累計))</t>
         </is>
       </c>
     </row>
@@ -3877,22 +3877,22 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>❌ 總表U欄空白未填</t>
+          <t>✅ 申報於 2026/10/27 存入 $25,361 (2026-10-21~2026-10-25累計)</t>
         </is>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>⏳ 待存入</t>
+          <t>➕ 溢存 +$845 (應收合 $24,516)</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>❌ 存摺未見入帳</t>
-        </is>
-      </c>
-      <c r="H13" s="20" t="inlineStr">
-        <is>
-          <t>🔴 門市未存 (留店未存)</t>
+          <t>⏳ 存摺尚未到帳/未更新</t>
+        </is>
+      </c>
+      <c r="H13" s="19" t="inlineStr">
+        <is>
+          <t>🟡 門市已申報 (待銀行入帳)</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>門市正常交班處理中，待總表申報或存款</t>
+          <t>【注意短溢：➕ 溢存 +$845 (應收合 $24,516)】總表已登記提存，待存摺更新自動結清 (申報於 2026/10/27 存入 $25,361 (2026-10-21~2026-10-25累計))</t>
         </is>
       </c>
     </row>
@@ -3925,22 +3925,22 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>❌ 總表U欄空白未填</t>
+          <t>✅ 申報於 2026/10/27 存入 $25,361 (2026-10-21~2026-10-25累計)</t>
         </is>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>⏳ 待存入</t>
+          <t>➕ 溢存 +$845 (應收合 $24,516)</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>❌ 存摺未見入帳</t>
-        </is>
-      </c>
-      <c r="H14" s="20" t="inlineStr">
-        <is>
-          <t>🔴 門市未存 (留店未存)</t>
+          <t>⏳ 存摺尚未到帳/未更新</t>
+        </is>
+      </c>
+      <c r="H14" s="19" t="inlineStr">
+        <is>
+          <t>🟡 門市已申報 (待銀行入帳)</t>
         </is>
       </c>
       <c r="I14" s="10" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>門市正常交班處理中，待總表申報或存款</t>
+          <t>【注意短溢：➕ 溢存 +$845 (應收合 $24,516)】總表已登記提存，待存摺更新自動結清 (申報於 2026/10/27 存入 $25,361 (2026-10-21~2026-10-25累計))</t>
         </is>
       </c>
     </row>

--- a/docs/output/本月對帳差額與應收餘額表_202610.xlsx
+++ b/docs/output/本月對帳差額與應收餘額表_202610.xlsx
@@ -652,14 +652,14 @@
         <v>203500</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>167270</v>
+        <v>191786</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>36230</v>
+        <v>11714</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>⏳ 實收現金 $203,500 / 已存現金 $167,270 ➔ 待入帳 $36,230</t>
+          <t>⏳ 實收現金 $203,500 / 已存現金 $191,786 ➔ 待入帳 $11,714</t>
         </is>
       </c>
     </row>
@@ -686,14 +686,14 @@
         <v>288646</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>226298</v>
+        <v>261323</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>62348</v>
+        <v>27323</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>⏳ 實收LINE Pay $288,646 / 已存 $226,298 ➔ 待入帳 $62,348</t>
+          <t>⏳ 實收LINE Pay $288,646 / 已存 $261,323 ➔ 待入帳 $27,323</t>
         </is>
       </c>
     </row>
@@ -754,14 +754,14 @@
         <v>3970</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1870</v>
+        <v>3213</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>2100</v>
+        <v>757</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>結算中（待撥 $2,100）</t>
+          <t>結算中（待撥 $757）</t>
         </is>
       </c>
     </row>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="E13" s="6" t="n">
-        <v>812457</v>
+        <v>874186</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
         </is>
       </c>
       <c r="E16" s="9" t="n">
-        <v>736270</v>
+        <v>797520</v>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -992,7 +992,7 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="52.5" customWidth="1" min="8" max="8"/>
-    <col width="118.5" customWidth="1" min="9" max="9"/>
+    <col width="121.5" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1463,33 +1463,33 @@
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>Uber Eats</t>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>現金存入</t>
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>26451</v>
+        <v>25361</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>26451</v>
+        <v>24516</v>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
-          <t>09/17~09/23外送款</t>
-        </is>
-      </c>
-      <c r="H12" s="17" t="inlineStr">
-        <is>
-          <t>跨月入帳 ➔ 歸屬 2026-09 月營收 (09/17~09/23)</t>
+          <t>2026-10-21~2026-10-25 多日累計</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="inlineStr">
+        <is>
+          <t>當期款項 ➔ 歸屬 2026-10 當月營收</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>沖銷 09/17~09/23外送款 Uber Eats 應收帳款</t>
+          <t>沖銷 2026-10-21~2026-10-25 多日累計 營業現金應收 (玉山 2026-10-27 存入) (銀行實收 $25,361，短溢調節 +$845)</t>
         </is>
       </c>
     </row>
@@ -1507,30 +1507,30 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>LINE Pay</t>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>Uber Eats</t>
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>5408</v>
+        <v>26451</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>5584</v>
+        <v>26451</v>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
-          <t>約09/29營業款</t>
+          <t>09/17~09/23外送款</t>
         </is>
       </c>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t>跨月入帳 ➔ 歸屬 2026-09 月營收</t>
+          <t>跨月入帳 ➔ 歸屬 2026-09 月營收 (09/17~09/23)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>沖銷 約09/29營業款 LINE Pay 應收帳款 (銀行實收 $5,408，內含平台手續費/稅 $176)</t>
+          <t>沖銷 09/17~09/23外送款 Uber Eats 應收帳款</t>
         </is>
       </c>
     </row>
@@ -1554,14 +1554,14 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>5261</v>
+        <v>5408</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>5261</v>
+        <v>5584</v>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>約09/30電支款</t>
+          <t>約09/29營業款</t>
         </is>
       </c>
       <c r="H14" s="17" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>沖銷 約09/30電支款 LINE Pay 應收帳款</t>
+          <t>沖銷 約09/29營業款 LINE Pay 應收帳款 (銀行實收 $5,408，內含平台手續費/稅 $176)</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
@@ -1595,14 +1595,14 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>3578</v>
+        <v>5261</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>3694</v>
+        <v>5261</v>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
-          <t>約09/30營業款</t>
+          <t>約09/30電支款</t>
         </is>
       </c>
       <c r="H15" s="17" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>沖銷 約09/30營業款 LINE Pay 應收帳款 (銀行實收 $3,578，內含平台手續費/稅 $116)</t>
+          <t>沖銷 約09/30電支款 LINE Pay 應收帳款</t>
         </is>
       </c>
     </row>
@@ -1636,24 +1636,24 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>6237</v>
+        <v>3578</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>6237</v>
+        <v>3694</v>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>約10/01電支款</t>
-        </is>
-      </c>
-      <c r="H16" s="15" t="inlineStr">
-        <is>
-          <t>當期款項 ➔ 歸屬 2026-10 當月營收</t>
+          <t>約09/30營業款</t>
+        </is>
+      </c>
+      <c r="H16" s="17" t="inlineStr">
+        <is>
+          <t>跨月入帳 ➔ 歸屬 2026-09 月營收</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>沖銷 約10/01電支款 LINE Pay 應收帳款</t>
+          <t>沖銷 約09/30營業款 LINE Pay 應收帳款 (銀行實收 $3,578，內含平台手續費/稅 $116)</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D17" s="15" t="inlineStr">
@@ -1677,14 +1677,14 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>4753</v>
+        <v>6237</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>4908</v>
+        <v>6237</v>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
-          <t>約10/01營業款</t>
+          <t>約10/01電支款</t>
         </is>
       </c>
       <c r="H17" s="15" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>沖銷 約10/01營業款 LINE Pay 應收帳款 (銀行實收 $4,753，內含平台手續費/稅 $155)</t>
+          <t>沖銷 約10/01電支款 LINE Pay 應收帳款</t>
         </is>
       </c>
     </row>
@@ -1718,14 +1718,14 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>6360</v>
+        <v>4753</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>6360</v>
+        <v>4908</v>
       </c>
       <c r="G18" s="13" t="inlineStr">
         <is>
-          <t>約10/04電支款</t>
+          <t>約10/01營業款</t>
         </is>
       </c>
       <c r="H18" s="15" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>沖銷 約10/04電支款 LINE Pay 應收帳款</t>
+          <t>沖銷 約10/01營業款 LINE Pay 應收帳款 (銀行實收 $4,753，內含平台手續費/稅 $155)</t>
         </is>
       </c>
     </row>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D19" s="15" t="inlineStr">
@@ -1759,14 +1759,14 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>16993</v>
+        <v>6360</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>17546</v>
+        <v>6360</v>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
-          <t>約10/03營業款</t>
+          <t>約10/04電支款</t>
         </is>
       </c>
       <c r="H19" s="15" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>沖銷 約10/03營業款 LINE Pay 應收帳款 (銀行實收 $16,993，內含平台手續費/稅 $553)</t>
+          <t>沖銷 約10/04電支款 LINE Pay 應收帳款</t>
         </is>
       </c>
     </row>
@@ -1800,14 +1800,14 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>30840</v>
+        <v>16993</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>30840</v>
+        <v>17546</v>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>約10/05電支款</t>
+          <t>約10/03營業款</t>
         </is>
       </c>
       <c r="H20" s="15" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>沖銷 約10/05電支款 LINE Pay 應收帳款</t>
+          <t>沖銷 約10/03營業款 LINE Pay 應收帳款 (銀行實收 $16,993，內含平台手續費/稅 $553)</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
@@ -1841,14 +1841,14 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>2668</v>
+        <v>30840</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>2755</v>
+        <v>30840</v>
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
-          <t>約10/05營業款</t>
+          <t>約10/05電支款</t>
         </is>
       </c>
       <c r="H21" s="15" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>沖銷 約10/05營業款 LINE Pay 應收帳款 (銀行實收 $2,668，內含平台手續費/稅 $87)</t>
+          <t>沖銷 約10/05電支款 LINE Pay 應收帳款</t>
         </is>
       </c>
     </row>
@@ -1882,14 +1882,14 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>6518</v>
+        <v>2668</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>6518</v>
+        <v>2755</v>
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
-          <t>約10/06電支款</t>
+          <t>約10/05營業款</t>
         </is>
       </c>
       <c r="H22" s="15" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>沖銷 約10/06電支款 LINE Pay 應收帳款</t>
+          <t>沖銷 約10/05營業款 LINE Pay 應收帳款 (銀行實收 $2,668，內含平台手續費/稅 $87)</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
@@ -1923,14 +1923,14 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>6908</v>
+        <v>6518</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>6908</v>
+        <v>6518</v>
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
-          <t>約10/07電支款</t>
+          <t>約10/06電支款</t>
         </is>
       </c>
       <c r="H23" s="15" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>沖銷 約10/07電支款 LINE Pay 應收帳款</t>
+          <t>沖銷 約10/06電支款 LINE Pay 應收帳款</t>
         </is>
       </c>
     </row>
@@ -1964,14 +1964,14 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>3075</v>
+        <v>6908</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>3175</v>
+        <v>6908</v>
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
-          <t>約10/06營業款</t>
+          <t>約10/07電支款</t>
         </is>
       </c>
       <c r="H24" s="15" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>沖銷 約10/06營業款 LINE Pay 應收帳款 (銀行實收 $3,075，內含平台手續費/稅 $100)</t>
+          <t>沖銷 約10/07電支款 LINE Pay 應收帳款</t>
         </is>
       </c>
     </row>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D25" s="15" t="inlineStr">
@@ -2005,14 +2005,14 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>7157</v>
+        <v>3075</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>7157</v>
+        <v>3175</v>
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
-          <t>約10/11電支款</t>
+          <t>約10/06營業款</t>
         </is>
       </c>
       <c r="H25" s="15" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>沖銷 約10/11電支款 LINE Pay 應收帳款</t>
+          <t>沖銷 約10/06營業款 LINE Pay 應收帳款 (銀行實收 $3,075，內含平台手續費/稅 $100)</t>
         </is>
       </c>
     </row>
@@ -2046,14 +2046,14 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>3005</v>
+        <v>7157</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>3103</v>
+        <v>7157</v>
       </c>
       <c r="G26" s="13" t="inlineStr">
         <is>
-          <t>約10/08營業款</t>
+          <t>約10/11電支款</t>
         </is>
       </c>
       <c r="H26" s="15" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>沖銷 約10/08營業款 LINE Pay 應收帳款 (銀行實收 $3,005，內含平台手續費/稅 $98)</t>
+          <t>沖銷 約10/11電支款 LINE Pay 應收帳款</t>
         </is>
       </c>
     </row>
@@ -2081,18 +2081,22 @@
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>偷訂</t>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>LINE Pay</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>1870</v>
+        <v>3005</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>1870</v>
-      </c>
-      <c r="G27" s="13" t="inlineStr"/>
+        <v>3103</v>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>約10/08營業款</t>
+        </is>
+      </c>
       <c r="H27" s="15" t="inlineStr">
         <is>
           <t>當期款項 ➔ 歸屬 2026-10 當月營收</t>
@@ -2100,7 +2104,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>沖銷 偷訂 應收帳款</t>
+          <t>沖銷 約10/08營業款 LINE Pay 應收帳款 (銀行實收 $3,005，內含平台手續費/稅 $98)</t>
         </is>
       </c>
     </row>
@@ -2115,25 +2119,21 @@
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="D28" s="15" t="inlineStr">
-        <is>
-          <t>LINE Pay</t>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="D28" s="18" t="inlineStr">
+        <is>
+          <t>偷訂</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>18335</v>
+        <v>1870</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>18931</v>
-      </c>
-      <c r="G28" s="13" t="inlineStr">
-        <is>
-          <t>約10/10營業款</t>
-        </is>
-      </c>
+        <v>1870</v>
+      </c>
+      <c r="G28" s="13" t="inlineStr"/>
       <c r="H28" s="15" t="inlineStr">
         <is>
           <t>當期款項 ➔ 歸屬 2026-10 當月營收</t>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>沖銷 約10/10營業款 LINE Pay 應收帳款 (銀行實收 $18,335，內含平台手續費/稅 $596)</t>
+          <t>沖銷 偷訂 應收帳款</t>
         </is>
       </c>
     </row>
@@ -2165,14 +2165,14 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>32962</v>
+        <v>18335</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>32962</v>
+        <v>18931</v>
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
-          <t>約10/12電支款</t>
+          <t>約10/10營業款</t>
         </is>
       </c>
       <c r="H29" s="15" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>沖銷 約10/12電支款 LINE Pay 應收帳款</t>
+          <t>沖銷 約10/10營業款 LINE Pay 應收帳款 (銀行實收 $18,335，內含平台手續費/稅 $596)</t>
         </is>
       </c>
     </row>
@@ -2197,7 +2197,7 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D30" s="15" t="inlineStr">
@@ -2206,14 +2206,14 @@
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>5780</v>
+        <v>32962</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>5780</v>
+        <v>32962</v>
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
-          <t>約10/13電支款</t>
+          <t>約10/12電支款</t>
         </is>
       </c>
       <c r="H30" s="15" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>沖銷 約10/13電支款 LINE Pay 應收帳款</t>
+          <t>沖銷 約10/12電支款 LINE Pay 應收帳款</t>
         </is>
       </c>
     </row>
@@ -2247,14 +2247,14 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>2926</v>
+        <v>5780</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>3021</v>
+        <v>5780</v>
       </c>
       <c r="G31" s="13" t="inlineStr">
         <is>
-          <t>約10/12營業款</t>
+          <t>約10/13電支款</t>
         </is>
       </c>
       <c r="H31" s="15" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>沖銷 約10/12營業款 LINE Pay 應收帳款 (銀行實收 $2,926，內含平台手續費/稅 $95)</t>
+          <t>沖銷 約10/13電支款 LINE Pay 應收帳款</t>
         </is>
       </c>
     </row>
@@ -2279,23 +2279,23 @@
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="D32" s="16" t="inlineStr">
-        <is>
-          <t>Uber Eats</t>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>LINE Pay</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>28996</v>
+        <v>2926</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>28996</v>
+        <v>3021</v>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
-          <t>10/01~10/07外送款</t>
+          <t>約10/12營業款</t>
         </is>
       </c>
       <c r="H32" s="15" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>沖銷 10/01~10/07外送款 Uber Eats 應收帳款</t>
+          <t>沖銷 約10/12營業款 LINE Pay 應收帳款 (銀行實收 $2,926，內含平台手續費/稅 $95)</t>
         </is>
       </c>
     </row>
@@ -2323,20 +2323,20 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="D33" s="15" t="inlineStr">
-        <is>
-          <t>LINE Pay</t>
+      <c r="D33" s="16" t="inlineStr">
+        <is>
+          <t>Uber Eats</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>7272</v>
+        <v>28996</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>7272</v>
+        <v>28996</v>
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
-          <t>約10/14電支款</t>
+          <t>10/01~10/07外送款</t>
         </is>
       </c>
       <c r="H33" s="15" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>沖銷 約10/14電支款 LINE Pay 應收帳款</t>
+          <t>沖銷 10/01~10/07外送款 Uber Eats 應收帳款</t>
         </is>
       </c>
     </row>
@@ -2370,14 +2370,14 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>2269</v>
+        <v>7272</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>2343</v>
+        <v>7272</v>
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
-          <t>約10/13營業款</t>
+          <t>約10/14電支款</t>
         </is>
       </c>
       <c r="H34" s="15" t="inlineStr">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>沖銷 約10/13營業款 LINE Pay 應收帳款 (銀行實收 $2,269，內含平台手續費/稅 $74)</t>
+          <t>沖銷 約10/14電支款 LINE Pay 應收帳款</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="D35" s="15" t="inlineStr">
@@ -2411,14 +2411,14 @@
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>7226</v>
+        <v>2269</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>7226</v>
+        <v>2343</v>
       </c>
       <c r="G35" s="13" t="inlineStr">
         <is>
-          <t>約10/15電支款</t>
+          <t>約10/13營業款</t>
         </is>
       </c>
       <c r="H35" s="15" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>沖銷 約10/15電支款 LINE Pay 應收帳款</t>
+          <t>沖銷 約10/13營業款 LINE Pay 應收帳款 (銀行實收 $2,269，內含平台手續費/稅 $74)</t>
         </is>
       </c>
     </row>
@@ -2452,14 +2452,14 @@
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>4262</v>
+        <v>7226</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>4401</v>
+        <v>7226</v>
       </c>
       <c r="G36" s="13" t="inlineStr">
         <is>
-          <t>約10/14營業款</t>
+          <t>約10/15電支款</t>
         </is>
       </c>
       <c r="H36" s="15" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>沖銷 約10/14營業款 LINE Pay 應收帳款 (銀行實收 $4,262，內含平台手續費/稅 $139)</t>
+          <t>沖銷 約10/15電支款 LINE Pay 應收帳款</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="D37" s="15" t="inlineStr">
@@ -2493,14 +2493,14 @@
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>2759</v>
+        <v>4262</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>2849</v>
+        <v>4401</v>
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
-          <t>約10/15營業款</t>
+          <t>約10/14營業款</t>
         </is>
       </c>
       <c r="H37" s="15" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>沖銷 約10/15營業款 LINE Pay 應收帳款 (銀行實收 $2,759，內含平台手續費/稅 $90)</t>
+          <t>沖銷 約10/14營業款 LINE Pay 應收帳款 (銀行實收 $4,262，內含平台手續費/稅 $139)</t>
         </is>
       </c>
     </row>
@@ -2534,14 +2534,14 @@
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>7337</v>
+        <v>2759</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>7337</v>
+        <v>2849</v>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
-          <t>約10/18電支款</t>
+          <t>約10/15營業款</t>
         </is>
       </c>
       <c r="H38" s="15" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>沖銷 約10/18電支款 LINE Pay 應收帳款</t>
+          <t>沖銷 約10/15營業款 LINE Pay 應收帳款 (銀行實收 $2,759，內含平台手續費/稅 $90)</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="D39" s="15" t="inlineStr">
@@ -2575,14 +2575,14 @@
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>8844</v>
+        <v>7337</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>9132</v>
+        <v>7337</v>
       </c>
       <c r="G39" s="13" t="inlineStr">
         <is>
-          <t>約10/17營業款</t>
+          <t>約10/18電支款</t>
         </is>
       </c>
       <c r="H39" s="15" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>沖銷 約10/17營業款 LINE Pay 應收帳款 (銀行實收 $8,844，內含平台手續費/稅 $288)</t>
+          <t>沖銷 約10/18電支款 LINE Pay 應收帳款</t>
         </is>
       </c>
     </row>
@@ -2616,14 +2616,14 @@
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>31812</v>
+        <v>8844</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>31812</v>
+        <v>9132</v>
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
-          <t>約10/19電支款</t>
+          <t>約10/17營業款</t>
         </is>
       </c>
       <c r="H40" s="15" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>沖銷 約10/19電支款 LINE Pay 應收帳款</t>
+          <t>沖銷 約10/17營業款 LINE Pay 應收帳款 (銀行實收 $8,844，內含平台手續費/稅 $288)</t>
         </is>
       </c>
     </row>
@@ -2643,38 +2643,38 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮(月下餐飲股份有限公司)</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="D41" s="11" t="inlineStr">
-        <is>
-          <t>現金存入</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="inlineStr">
+        <is>
+          <t>LINE Pay</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>11340</v>
+        <v>31812</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>11340</v>
+        <v>31812</v>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
-          <t>2026-09-30 (上月跨月款)</t>
-        </is>
-      </c>
-      <c r="H41" s="17" t="inlineStr">
-        <is>
-          <t>跨月入帳 ➔ 歸屬 2026-09 月營收 (9/30款)</t>
+          <t>約10/19電支款</t>
+        </is>
+      </c>
+      <c r="H41" s="15" t="inlineStr">
+        <is>
+          <t>當期款項 ➔ 歸屬 2026-10 當月營收</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>沖銷 2026-09-30 (上月跨月款) 營業現金應收 (玉山 2026-10-01 存入)</t>
+          <t>沖銷 約10/19電支款 LINE Pay 應收帳款</t>
         </is>
       </c>
     </row>
@@ -2684,28 +2684,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮(月下餐飲股份有限公司)</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="D42" s="11" t="inlineStr">
-        <is>
-          <t>現金存入</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="D42" s="15" t="inlineStr">
+        <is>
+          <t>LINE Pay</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>9880</v>
+        <v>4085</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>9880</v>
+        <v>4085</v>
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>約10/20電支款</t>
         </is>
       </c>
       <c r="H42" s="15" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>沖銷 2026-10-01 營業現金應收 (玉山 2026-10-02 存入)</t>
+          <t>沖銷 約10/20電支款 LINE Pay 應收帳款</t>
         </is>
       </c>
     </row>
@@ -2725,28 +2725,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮(月下餐飲股份有限公司)</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="D43" s="11" t="inlineStr">
-        <is>
-          <t>現金存入</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="D43" s="15" t="inlineStr">
+        <is>
+          <t>LINE Pay</t>
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>57305</v>
+        <v>2993</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>57300</v>
+        <v>3090</v>
       </c>
       <c r="G43" s="13" t="inlineStr">
         <is>
-          <t>2026-10-02~2026-10-04 多日累計</t>
+          <t>約10/19營業款</t>
         </is>
       </c>
       <c r="H43" s="15" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>沖銷 2026-10-02~2026-10-04 多日累計 營業現金應收 (玉山 2026-10-05 存入) (銀行實收 $57,305，短溢調節 +$5)</t>
+          <t>沖銷 約10/19營業款 LINE Pay 應收帳款 (銀行實收 $2,993，內含平台手續費/稅 $97)</t>
         </is>
       </c>
     </row>
@@ -2766,28 +2766,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮(月下餐飲股份有限公司)</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="D44" s="11" t="inlineStr">
-        <is>
-          <t>現金存入</t>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="D44" s="15" t="inlineStr">
+        <is>
+          <t>LINE Pay</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>9520</v>
+        <v>8202</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>9520</v>
+        <v>8202</v>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>約10/21電支款</t>
         </is>
       </c>
       <c r="H44" s="15" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>沖銷 2026-10-05 營業現金應收 (玉山 2026-10-06 存入)</t>
+          <t>沖銷 約10/21電支款 LINE Pay 應收帳款</t>
         </is>
       </c>
     </row>
@@ -2807,28 +2807,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮(月下餐飲股份有限公司)</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="D45" s="11" t="inlineStr">
-        <is>
-          <t>現金存入</t>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="D45" s="15" t="inlineStr">
+        <is>
+          <t>LINE Pay</t>
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>27570</v>
+        <v>2614</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>27570</v>
+        <v>2699</v>
       </c>
       <c r="G45" s="13" t="inlineStr">
         <is>
-          <t>2026-10-06~2026-10-07 多日累計</t>
+          <t>約10/20營業款</t>
         </is>
       </c>
       <c r="H45" s="15" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>沖銷 2026-10-06~2026-10-07 多日累計 營業現金應收 (玉山 2026-10-08 存入)</t>
+          <t>沖銷 約10/20營業款 LINE Pay 應收帳款 (銀行實收 $2,614，內含平台手續費/稅 $85)</t>
         </is>
       </c>
     </row>
@@ -2848,28 +2848,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮(月下餐飲股份有限公司)</t>
         </is>
       </c>
       <c r="C46" s="10" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="D46" s="11" t="inlineStr">
-        <is>
-          <t>現金存入</t>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D46" s="15" t="inlineStr">
+        <is>
+          <t>LINE Pay</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>73748</v>
+        <v>3994</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>73748</v>
+        <v>4124</v>
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
-          <t>2026-10-08~2026-10-11 多日累計</t>
+          <t>約10/24營業款</t>
         </is>
       </c>
       <c r="H46" s="15" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>沖銷 2026-10-08~2026-10-11 多日累計 營業現金應收 (玉山 2026-10-12 存入)</t>
+          <t>沖銷 約10/24營業款 LINE Pay 應收帳款 (銀行實收 $3,994，內含平台手續費/稅 $130)</t>
         </is>
       </c>
     </row>
@@ -2889,28 +2889,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮(月下餐飲股份有限公司)</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="D47" s="11" t="inlineStr">
-        <is>
-          <t>現金存入</t>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D47" s="15" t="inlineStr">
+        <is>
+          <t>LINE Pay</t>
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>12400</v>
+        <v>1667</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>12400</v>
+        <v>1721</v>
       </c>
       <c r="G47" s="13" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>約10/24營業款</t>
         </is>
       </c>
       <c r="H47" s="15" t="inlineStr">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>沖銷 2026-10-12 營業現金應收 (玉山 2026-10-13 存入)</t>
+          <t>沖銷 約10/24營業款 LINE Pay 應收帳款 (銀行實收 $1,667，內含平台手續費/稅 $54)</t>
         </is>
       </c>
     </row>
@@ -2930,28 +2930,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮(月下餐飲股份有限公司)</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="D48" s="11" t="inlineStr">
-        <is>
-          <t>現金存入</t>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D48" s="15" t="inlineStr">
+        <is>
+          <t>LINE Pay</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>18810</v>
+        <v>6789</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>18810</v>
+        <v>6789</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>約10/26電支款</t>
         </is>
       </c>
       <c r="H48" s="15" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>沖銷 2026-10-13 營業現金應收 (玉山 2026-10-14 存入)</t>
+          <t>沖銷 約10/26電支款 LINE Pay 應收帳款</t>
         </is>
       </c>
     </row>
@@ -2971,38 +2971,38 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮(月下餐飲股份有限公司)</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="D49" s="16" t="inlineStr">
-        <is>
-          <t>Uber Eats</t>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D49" s="15" t="inlineStr">
+        <is>
+          <t>LINE Pay</t>
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>14615</v>
+        <v>4681</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>14615</v>
+        <v>4681</v>
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
-          <t>09/17~09/23外送款</t>
-        </is>
-      </c>
-      <c r="H49" s="17" t="inlineStr">
-        <is>
-          <t>跨月入帳 ➔ 歸屬 2026-09 月營收 (09/17~09/23)</t>
+          <t>約10/26電支款</t>
+        </is>
+      </c>
+      <c r="H49" s="15" t="inlineStr">
+        <is>
+          <t>當期款項 ➔ 歸屬 2026-10 當月營收</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>沖銷 09/17~09/23外送款 Uber Eats 應收帳款</t>
+          <t>沖銷 約10/26電支款 LINE Pay 應收帳款</t>
         </is>
       </c>
     </row>
@@ -3012,30 +3012,26 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮(月下餐飲股份有限公司)</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="D50" s="15" t="inlineStr">
-        <is>
-          <t>LINE Pay</t>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D50" s="18" t="inlineStr">
+        <is>
+          <t>偷訂</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>14009</v>
+        <v>1343</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>14465</v>
-      </c>
-      <c r="G50" s="13" t="inlineStr">
-        <is>
-          <t>約10/03營業款</t>
-        </is>
-      </c>
+        <v>1343</v>
+      </c>
+      <c r="G50" s="13" t="inlineStr"/>
       <c r="H50" s="15" t="inlineStr">
         <is>
           <t>當期款項 ➔ 歸屬 2026-10 當月營收</t>
@@ -3043,7 +3039,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>沖銷 約10/03營業款 LINE Pay 應收帳款 (銀行實收 $14,009，內含平台手續費/稅 $456)</t>
+          <t>沖銷 偷訂 應收帳款</t>
         </is>
       </c>
     </row>
@@ -3058,33 +3054,33 @@
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="D51" s="15" t="inlineStr">
-        <is>
-          <t>LINE Pay</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>現金存入</t>
         </is>
       </c>
       <c r="E51" s="12" t="n">
-        <v>29827</v>
+        <v>11340</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>29827</v>
+        <v>11340</v>
       </c>
       <c r="G51" s="13" t="inlineStr">
         <is>
-          <t>約10/05電支款</t>
-        </is>
-      </c>
-      <c r="H51" s="15" t="inlineStr">
-        <is>
-          <t>當期款項 ➔ 歸屬 2026-10 當月營收</t>
+          <t>2026-09-30 (上月跨月款)</t>
+        </is>
+      </c>
+      <c r="H51" s="17" t="inlineStr">
+        <is>
+          <t>跨月入帳 ➔ 歸屬 2026-09 月營收 (9/30款)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>沖銷 約10/05電支款 LINE Pay 應收帳款</t>
+          <t>沖銷 2026-09-30 (上月跨月款) 營業現金應收 (玉山 2026-10-01 存入)</t>
         </is>
       </c>
     </row>
@@ -3099,33 +3095,33 @@
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="D52" s="17" t="inlineStr">
-        <is>
-          <t>Foodpanda</t>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>現金存入</t>
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>7255</v>
+        <v>9880</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>7255</v>
+        <v>9880</v>
       </c>
       <c r="G52" s="13" t="inlineStr">
         <is>
-          <t>上月下半月(16~30日)外送款</t>
-        </is>
-      </c>
-      <c r="H52" s="17" t="inlineStr">
-        <is>
-          <t>跨月入帳 ➔ 歸屬 2026-09 月營收 (9月下半月款)</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="H52" s="15" t="inlineStr">
+        <is>
+          <t>當期款項 ➔ 歸屬 2026-10 當月營收</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>沖銷 上月下半月(16~30日)外送款 Foodpanda 應收帳款</t>
+          <t>沖銷 2026-10-01 營業現金應收 (玉山 2026-10-02 存入)</t>
         </is>
       </c>
     </row>
@@ -3140,23 +3136,23 @@
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="D53" s="15" t="inlineStr">
-        <is>
-          <t>LINE Pay</t>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>現金存入</t>
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>18024</v>
+        <v>57305</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>18610</v>
+        <v>57300</v>
       </c>
       <c r="G53" s="13" t="inlineStr">
         <is>
-          <t>約10/10營業款</t>
+          <t>2026-10-02~2026-10-04 多日累計</t>
         </is>
       </c>
       <c r="H53" s="15" t="inlineStr">
@@ -3166,7 +3162,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>沖銷 約10/10營業款 LINE Pay 應收帳款 (銀行實收 $18,024，內含平台手續費/稅 $586)</t>
+          <t>沖銷 2026-10-02~2026-10-04 多日累計 營業現金應收 (玉山 2026-10-05 存入) (銀行實收 $57,305，短溢調節 +$5)</t>
         </is>
       </c>
     </row>
@@ -3181,23 +3177,23 @@
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="D54" s="15" t="inlineStr">
-        <is>
-          <t>LINE Pay</t>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>現金存入</t>
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>32130</v>
+        <v>9520</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>32130</v>
+        <v>9520</v>
       </c>
       <c r="G54" s="13" t="inlineStr">
         <is>
-          <t>約10/12電支款</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H54" s="15" t="inlineStr">
@@ -3207,7 +3203,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>沖銷 約10/12電支款 LINE Pay 應收帳款</t>
+          <t>沖銷 2026-10-05 營業現金應收 (玉山 2026-10-06 存入)</t>
         </is>
       </c>
     </row>
@@ -3222,31 +3218,441 @@
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>現金存入</t>
+        </is>
+      </c>
+      <c r="E55" s="12" t="n">
+        <v>27570</v>
+      </c>
+      <c r="F55" s="12" t="n">
+        <v>27570</v>
+      </c>
+      <c r="G55" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-06~2026-10-07 多日累計</t>
+        </is>
+      </c>
+      <c r="H55" s="15" t="inlineStr">
+        <is>
+          <t>當期款項 ➔ 歸屬 2026-10 當月營收</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>沖銷 2026-10-06~2026-10-07 多日累計 營業現金應收 (玉山 2026-10-08 存入)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>現金存入</t>
+        </is>
+      </c>
+      <c r="E56" s="12" t="n">
+        <v>73748</v>
+      </c>
+      <c r="F56" s="12" t="n">
+        <v>73748</v>
+      </c>
+      <c r="G56" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-08~2026-10-11 多日累計</t>
+        </is>
+      </c>
+      <c r="H56" s="15" t="inlineStr">
+        <is>
+          <t>當期款項 ➔ 歸屬 2026-10 當月營收</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>沖銷 2026-10-08~2026-10-11 多日累計 營業現金應收 (玉山 2026-10-12 存入)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>現金存入</t>
+        </is>
+      </c>
+      <c r="E57" s="12" t="n">
+        <v>12400</v>
+      </c>
+      <c r="F57" s="12" t="n">
+        <v>12400</v>
+      </c>
+      <c r="G57" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="H57" s="15" t="inlineStr">
+        <is>
+          <t>當期款項 ➔ 歸屬 2026-10 當月營收</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>沖銷 2026-10-12 營業現金應收 (玉山 2026-10-13 存入)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>現金存入</t>
+        </is>
+      </c>
+      <c r="E58" s="12" t="n">
+        <v>18810</v>
+      </c>
+      <c r="F58" s="12" t="n">
+        <v>18810</v>
+      </c>
+      <c r="G58" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="H58" s="15" t="inlineStr">
+        <is>
+          <t>當期款項 ➔ 歸屬 2026-10 當月營收</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>沖銷 2026-10-13 營業現金應收 (玉山 2026-10-14 存入)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D59" s="16" t="inlineStr">
+        <is>
+          <t>Uber Eats</t>
+        </is>
+      </c>
+      <c r="E59" s="12" t="n">
+        <v>14615</v>
+      </c>
+      <c r="F59" s="12" t="n">
+        <v>14615</v>
+      </c>
+      <c r="G59" s="13" t="inlineStr">
+        <is>
+          <t>09/17~09/23外送款</t>
+        </is>
+      </c>
+      <c r="H59" s="17" t="inlineStr">
+        <is>
+          <t>跨月入帳 ➔ 歸屬 2026-09 月營收 (09/17~09/23)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>沖銷 09/17~09/23外送款 Uber Eats 應收帳款</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D60" s="15" t="inlineStr">
+        <is>
+          <t>LINE Pay</t>
+        </is>
+      </c>
+      <c r="E60" s="12" t="n">
+        <v>14009</v>
+      </c>
+      <c r="F60" s="12" t="n">
+        <v>14465</v>
+      </c>
+      <c r="G60" s="13" t="inlineStr">
+        <is>
+          <t>約10/03營業款</t>
+        </is>
+      </c>
+      <c r="H60" s="15" t="inlineStr">
+        <is>
+          <t>當期款項 ➔ 歸屬 2026-10 當月營收</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>沖銷 約10/03營業款 LINE Pay 應收帳款 (銀行實收 $14,009，內含平台手續費/稅 $456)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D61" s="15" t="inlineStr">
+        <is>
+          <t>LINE Pay</t>
+        </is>
+      </c>
+      <c r="E61" s="12" t="n">
+        <v>29827</v>
+      </c>
+      <c r="F61" s="12" t="n">
+        <v>29827</v>
+      </c>
+      <c r="G61" s="13" t="inlineStr">
+        <is>
+          <t>約10/05電支款</t>
+        </is>
+      </c>
+      <c r="H61" s="15" t="inlineStr">
+        <is>
+          <t>當期款項 ➔ 歸屬 2026-10 當月營收</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>沖銷 約10/05電支款 LINE Pay 應收帳款</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="D62" s="17" t="inlineStr">
+        <is>
+          <t>Foodpanda</t>
+        </is>
+      </c>
+      <c r="E62" s="12" t="n">
+        <v>7255</v>
+      </c>
+      <c r="F62" s="12" t="n">
+        <v>7255</v>
+      </c>
+      <c r="G62" s="13" t="inlineStr">
+        <is>
+          <t>上月下半月(16~30日)外送款</t>
+        </is>
+      </c>
+      <c r="H62" s="17" t="inlineStr">
+        <is>
+          <t>跨月入帳 ➔ 歸屬 2026-09 月營收 (9月下半月款)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>沖銷 上月下半月(16~30日)外送款 Foodpanda 應收帳款</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D63" s="15" t="inlineStr">
+        <is>
+          <t>LINE Pay</t>
+        </is>
+      </c>
+      <c r="E63" s="12" t="n">
+        <v>18024</v>
+      </c>
+      <c r="F63" s="12" t="n">
+        <v>18610</v>
+      </c>
+      <c r="G63" s="13" t="inlineStr">
+        <is>
+          <t>約10/10營業款</t>
+        </is>
+      </c>
+      <c r="H63" s="15" t="inlineStr">
+        <is>
+          <t>當期款項 ➔ 歸屬 2026-10 當月營收</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>沖銷 約10/10營業款 LINE Pay 應收帳款 (銀行實收 $18,024，內含平台手續費/稅 $586)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D64" s="15" t="inlineStr">
+        <is>
+          <t>LINE Pay</t>
+        </is>
+      </c>
+      <c r="E64" s="12" t="n">
+        <v>32130</v>
+      </c>
+      <c r="F64" s="12" t="n">
+        <v>32130</v>
+      </c>
+      <c r="G64" s="13" t="inlineStr">
+        <is>
+          <t>約10/12電支款</t>
+        </is>
+      </c>
+      <c r="H64" s="15" t="inlineStr">
+        <is>
+          <t>當期款項 ➔ 歸屬 2026-10 當月營收</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>沖銷 約10/12電支款 LINE Pay 應收帳款</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="D55" s="16" t="inlineStr">
+      <c r="D65" s="16" t="inlineStr">
         <is>
           <t>Uber Eats</t>
         </is>
       </c>
-      <c r="E55" s="12" t="n">
+      <c r="E65" s="12" t="n">
         <v>5301</v>
       </c>
-      <c r="F55" s="12" t="n">
+      <c r="F65" s="12" t="n">
         <v>5301</v>
       </c>
-      <c r="G55" s="13" t="inlineStr">
+      <c r="G65" s="13" t="inlineStr">
         <is>
           <t>10/01~10/07外送款</t>
         </is>
       </c>
-      <c r="H55" s="15" t="inlineStr">
-        <is>
-          <t>當期款項 ➔ 歸屬 2026-10 當月營收</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
+      <c r="H65" s="15" t="inlineStr">
+        <is>
+          <t>當期款項 ➔ 歸屬 2026-10 當月營收</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
         <is>
           <t>沖銷 10/01~10/07外送款 Uber Eats 應收帳款</t>
         </is>
@@ -3263,7 +3669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3720,7 +4126,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>月宮 (月下餐飲)</t>
+          <t>隨意小吃</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -3729,26 +4135,26 @@
         </is>
       </c>
       <c r="D10" s="12" t="n">
-        <v>6977</v>
+        <v>10820</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>✅ 申報於 2026/10/27 存入 $25,361 (2026-10-21~2026-10-25累計)</t>
+          <t>❌ 總表U欄空白未填</t>
         </is>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>➕ 溢存 +$845 (應收合 $24,516)</t>
+          <t>⏳ 待存入</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>⏳ 存摺尚未到帳/未更新</t>
-        </is>
-      </c>
-      <c r="H10" s="19" t="inlineStr">
-        <is>
-          <t>🟡 門市已申報 (待銀行入帳)</t>
+          <t>❌ 存摺未見入帳</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>🔴 門市未存 (留店未存)</t>
         </is>
       </c>
       <c r="I10" s="10" t="inlineStr">
@@ -3758,7 +4164,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>【注意短溢：➕ 溢存 +$845 (應收合 $24,516)】總表已登記提存，待存摺更新自動結清 (申報於 2026/10/27 存入 $25,361 (2026-10-21~2026-10-25累計))</t>
+          <t>門市正常交班處理中，待總表申報或存款</t>
         </is>
       </c>
     </row>
@@ -3768,16 +4174,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮 (月下餐飲)</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D11" s="12" t="n">
-        <v>10820</v>
+        <v>5243</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -3801,7 +4207,7 @@
       </c>
       <c r="I11" s="10" t="inlineStr">
         <is>
-          <t>1 天</t>
+          <t>0 天</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -3816,7 +4222,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>月宮 (月下餐飲)</t>
+          <t>隨意小吃</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
@@ -3825,26 +4231,26 @@
         </is>
       </c>
       <c r="D12" s="12" t="n">
-        <v>5728</v>
+        <v>13890</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>✅ 申報於 2026/10/27 存入 $25,361 (2026-10-21~2026-10-25累計)</t>
+          <t>❌ 總表U欄空白未填</t>
         </is>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>➕ 溢存 +$845 (應收合 $24,516)</t>
+          <t>⏳ 待存入</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>⏳ 存摺尚未到帳/未更新</t>
-        </is>
-      </c>
-      <c r="H12" s="19" t="inlineStr">
-        <is>
-          <t>🟡 門市已申報 (待銀行入帳)</t>
+          <t>❌ 存摺未見入帳</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>🔴 門市未存 (留店未存)</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr">
@@ -3854,7 +4260,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>【注意短溢：➕ 溢存 +$845 (應收合 $24,516)】總表已登記提存，待存摺更新自動結清 (申報於 2026/10/27 存入 $25,361 (2026-10-21~2026-10-25累計))</t>
+          <t>門市正常交班處理中，待總表申報或存款</t>
         </is>
       </c>
     </row>
@@ -3864,35 +4270,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>月宮 (月下餐飲)</t>
+          <t>隨意小吃</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="D13" s="12" t="n">
-        <v>1935</v>
+        <v>18100</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>✅ 申報於 2026/10/27 存入 $25,361 (2026-10-21~2026-10-25累計)</t>
+          <t>❌ 總表U欄空白未填</t>
         </is>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>➕ 溢存 +$845 (應收合 $24,516)</t>
+          <t>⏳ 待存入</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>⏳ 存摺尚未到帳/未更新</t>
-        </is>
-      </c>
-      <c r="H13" s="19" t="inlineStr">
-        <is>
-          <t>🟡 門市已申報 (待銀行入帳)</t>
+          <t>❌ 存摺未見入帳</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>🔴 門市未存 (留店未存)</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr">
@@ -3902,7 +4308,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>【注意短溢：➕ 溢存 +$845 (應收合 $24,516)】總表已登記提存，待存摺更新自動結清 (申報於 2026/10/27 存入 $25,361 (2026-10-21~2026-10-25累計))</t>
+          <t>門市正常交班處理中，待總表申報或存款</t>
         </is>
       </c>
     </row>
@@ -3912,35 +4318,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>月宮 (月下餐飲)</t>
+          <t>隨意小吃</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="D14" s="12" t="n">
-        <v>9876</v>
+        <v>14830</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>✅ 申報於 2026/10/27 存入 $25,361 (2026-10-21~2026-10-25累計)</t>
+          <t>❌ 總表U欄空白未填</t>
         </is>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>➕ 溢存 +$845 (應收合 $24,516)</t>
+          <t>⏳ 待存入</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>⏳ 存摺尚未到帳/未更新</t>
-        </is>
-      </c>
-      <c r="H14" s="19" t="inlineStr">
-        <is>
-          <t>🟡 門市已申報 (待銀行入帳)</t>
+          <t>❌ 存摺未見入帳</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>🔴 門市未存 (留店未存)</t>
         </is>
       </c>
       <c r="I14" s="10" t="inlineStr">
@@ -3949,198 +4355,6 @@
         </is>
       </c>
       <c r="J14" t="inlineStr">
-        <is>
-          <t>【注意短溢：➕ 溢存 +$845 (應收合 $24,516)】總表已登記提存，待存摺更新自動結清 (申報於 2026/10/27 存入 $25,361 (2026-10-21~2026-10-25累計))</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="10" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>月宮 (月下餐飲)</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="D15" s="12" t="n">
-        <v>5243</v>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>❌ 總表U欄空白未填</t>
-        </is>
-      </c>
-      <c r="F15" s="10" t="inlineStr">
-        <is>
-          <t>⏳ 待存入</t>
-        </is>
-      </c>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>❌ 存摺未見入帳</t>
-        </is>
-      </c>
-      <c r="H15" s="20" t="inlineStr">
-        <is>
-          <t>🔴 門市未存 (留店未存)</t>
-        </is>
-      </c>
-      <c r="I15" s="10" t="inlineStr">
-        <is>
-          <t>0 天</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>門市正常交班處理中，待總表申報或存款</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>隨意小吃</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="n">
-        <v>13890</v>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>❌ 總表U欄空白未填</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
-          <t>⏳ 待存入</t>
-        </is>
-      </c>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>❌ 存摺未見入帳</t>
-        </is>
-      </c>
-      <c r="H16" s="20" t="inlineStr">
-        <is>
-          <t>🔴 門市未存 (留店未存)</t>
-        </is>
-      </c>
-      <c r="I16" s="10" t="inlineStr">
-        <is>
-          <t>0 天</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>門市正常交班處理中，待總表申報或存款</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>隨意小吃</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-25</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="n">
-        <v>18100</v>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>❌ 總表U欄空白未填</t>
-        </is>
-      </c>
-      <c r="F17" s="10" t="inlineStr">
-        <is>
-          <t>⏳ 待存入</t>
-        </is>
-      </c>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t>❌ 存摺未見入帳</t>
-        </is>
-      </c>
-      <c r="H17" s="20" t="inlineStr">
-        <is>
-          <t>🔴 門市未存 (留店未存)</t>
-        </is>
-      </c>
-      <c r="I17" s="10" t="inlineStr">
-        <is>
-          <t>0 天</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>門市正常交班處理中，待總表申報或存款</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>隨意小吃</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="n">
-        <v>14830</v>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>❌ 總表U欄空白未填</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>⏳ 待存入</t>
-        </is>
-      </c>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>❌ 存摺未見入帳</t>
-        </is>
-      </c>
-      <c r="H18" s="20" t="inlineStr">
-        <is>
-          <t>🔴 門市未存 (留店未存)</t>
-        </is>
-      </c>
-      <c r="I18" s="10" t="inlineStr">
-        <is>
-          <t>0 天</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
         <is>
           <t>門市正常交班處理中，待總表申報或存款</t>
         </is>

--- a/docs/output/本月對帳差額與應收餘額表_202610.xlsx
+++ b/docs/output/本月對帳差額與應收餘額表_202610.xlsx
@@ -646,20 +646,20 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>203500</v>
+        <v>209565</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>203500</v>
+        <v>209565</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>191786</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>11714</v>
+        <v>17779</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>⏳ 實收現金 $203,500 / 已存現金 $191,786 ➔ 待入帳 $11,714</t>
+          <t>⏳ 實收現金 $209,565 / 已存現金 $191,786 ➔ 待入帳 $17,779</t>
         </is>
       </c>
     </row>
@@ -680,20 +680,20 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>295484</v>
+        <v>303640</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>288646</v>
+        <v>296613</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>261323</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>27323</v>
+        <v>35290</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>⏳ 實收LINE Pay $288,646 / 已存 $261,323 ➔ 待入帳 $27,323</t>
+          <t>⏳ 實收LINE Pay $296,613 / 已存 $261,323 ➔ 待入帳 $35,290</t>
         </is>
       </c>
     </row>
@@ -714,20 +714,20 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>60856</v>
+        <v>64003</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>40774</v>
+        <v>42882</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>28996</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>11778</v>
+        <v>13886</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>⏳ 實收Uber Eats $40,774 / 已存 $28,996 ➔ 待入帳 $11,778</t>
+          <t>⏳ 實收Uber Eats $42,882 / 已存 $28,996 ➔ 待入帳 $13,886</t>
         </is>
       </c>
     </row>
@@ -782,20 +782,20 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>369237</v>
+        <v>384727</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>369237</v>
+        <v>384727</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>209228</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>160009</v>
+        <v>175499</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>⏳ 實收現金 $369,237 / 已存現金 $209,228 ➔ 待入帳 $160,009</t>
+          <t>⏳ 實收現金 $384,727 / 已存現金 $209,228 ➔ 待入帳 $175,499</t>
         </is>
       </c>
     </row>
@@ -816,20 +816,20 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>187672</v>
+        <v>194432</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>183329</v>
+        <v>189933</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>93990</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>89339</v>
+        <v>95943</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>⏳ 實收LINE Pay $183,329 / 已存 $93,990 ➔ 待入帳 $89,339</t>
+          <t>⏳ 實收LINE Pay $189,933 / 已存 $93,990 ➔ 待入帳 $95,943</t>
         </is>
       </c>
     </row>
@@ -850,20 +850,20 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>17385</v>
+        <v>20140</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>11990</v>
+        <v>13890</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>5301</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>6689</v>
+        <v>8589</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>⏳ 實收Uber Eats $11,990 / 已存 $5,301 ➔ 待入帳 $6,689</t>
+          <t>⏳ 實收Uber Eats $13,890 / 已存 $5,301 ➔ 待入帳 $8,589</t>
         </is>
       </c>
     </row>
@@ -884,20 +884,20 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>18722</v>
+        <v>19080</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>12431</v>
+        <v>12669</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>12431</v>
+        <v>12669</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>⏳ 實收Foodpanda $12,431 / 已存 $0 ➔ 待入帳 $12,431</t>
+          <t>⏳ 實收Foodpanda $12,669 / 已存 $0 ➔ 待入帳 $12,669</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4222,16 +4222,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮 (月下餐飲)</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="D12" s="12" t="n">
-        <v>13890</v>
+        <v>6065</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
@@ -4275,11 +4275,11 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D13" s="12" t="n">
-        <v>18100</v>
+        <v>13890</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
@@ -4323,38 +4323,134 @@
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="n">
+        <v>18100</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>❌ 總表U欄空白未填</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>⏳ 待存入</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>❌ 存摺未見入帳</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>🔴 門市未存 (留店未存)</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>0 天</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>門市正常交班處理中，待總表申報或存款</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="D14" s="12" t="n">
+      <c r="D15" s="12" t="n">
         <v>14830</v>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>❌ 總表U欄空白未填</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>⏳ 待存入</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="G15" s="10" t="inlineStr">
         <is>
           <t>❌ 存摺未見入帳</t>
         </is>
       </c>
-      <c r="H14" s="20" t="inlineStr">
+      <c r="H15" s="20" t="inlineStr">
         <is>
           <t>🔴 門市未存 (留店未存)</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="I15" s="10" t="inlineStr">
         <is>
           <t>0 天</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>門市正常交班處理中，待總表申報或存款</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>15490</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>❌ 總表U欄空白未填</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>⏳ 待存入</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>❌ 存摺未見入帳</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>🔴 門市未存 (留店未存)</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>0 天</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>門市正常交班處理中，待總表申報或存款</t>
         </is>
@@ -4383,7 +4479,7 @@
     <col width="19.5" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="22.5" customWidth="1" min="9" max="9"/>
-    <col width="64.5" customWidth="1" min="10" max="10"/>
+    <col width="67.5" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4460,13 +4556,13 @@
         </is>
       </c>
       <c r="E2" s="12" t="n">
-        <v>295484</v>
+        <v>303640</v>
       </c>
       <c r="F2" s="12" t="n">
-        <v>6838</v>
+        <v>7027</v>
       </c>
       <c r="G2" s="12" t="n">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="H2" s="12" t="n">
         <v>0</v>
@@ -4478,7 +4574,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>連加網路 (99024139) 手續費約 $6,838（含可扣抵進項稅額 $326）</t>
+          <t>連加網路 (99024139) 手續費約 $7,027（含可扣抵進項稅額 $335）</t>
         </is>
       </c>
     </row>
@@ -4504,13 +4600,13 @@
         </is>
       </c>
       <c r="E3" s="12" t="n">
-        <v>60856</v>
+        <v>64003</v>
       </c>
       <c r="F3" s="12" t="n">
-        <v>20082</v>
+        <v>21121</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>956</v>
+        <v>1006</v>
       </c>
       <c r="H3" s="12" t="n">
         <v>0</v>
@@ -4522,7 +4618,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>優步科技 (83118125) 手續費發票約 $20,082（含可扣抵稅額 $956）</t>
+          <t>優步科技 (83118125) 手續費發票約 $21,121（含可扣抵稅額 $1,006）</t>
         </is>
       </c>
     </row>
@@ -4548,13 +4644,13 @@
         </is>
       </c>
       <c r="E4" s="12" t="n">
-        <v>187672</v>
+        <v>194432</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>4343</v>
+        <v>4499</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="H4" s="12" t="n">
         <v>0</v>
@@ -4566,7 +4662,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>連加網路 (99024139) 手續費約 $4,343（含可扣抵進項稅額 $207）</t>
+          <t>連加網路 (99024139) 手續費約 $4,499（含可扣抵進項稅額 $214）</t>
         </is>
       </c>
     </row>
@@ -4592,13 +4688,13 @@
         </is>
       </c>
       <c r="E5" s="12" t="n">
-        <v>17385</v>
+        <v>20140</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>5395</v>
+        <v>6250</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>257</v>
+        <v>298</v>
       </c>
       <c r="H5" s="12" t="n">
         <v>0</v>
@@ -4610,7 +4706,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>優步科技 (83118125) 手續費發票約 $5,395（含可扣抵稅額 $257）</t>
+          <t>優步科技 (83118125) 手續費發票約 $6,250（含可扣抵稅額 $298）</t>
         </is>
       </c>
     </row>
@@ -4636,13 +4732,13 @@
         </is>
       </c>
       <c r="E6" s="12" t="n">
-        <v>18722</v>
+        <v>19080</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>6291</v>
+        <v>6411</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="H6" s="12" t="n">
         <v>0</v>
@@ -4654,7 +4750,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>富胖達 (53075607) 手續費發票約 $6,291（含可扣抵稅額 $300）</t>
+          <t>富胖達 (53075607) 手續費發票約 $6,411（含可扣抵稅額 $305）</t>
         </is>
       </c>
     </row>

--- a/docs/output/本月對帳差額與應收餘額表_202610.xlsx
+++ b/docs/output/本月對帳差額與應收餘額表_202610.xlsx
@@ -646,20 +646,20 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>209565</v>
+        <v>230206</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>209565</v>
+        <v>230206</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>191786</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>17779</v>
+        <v>38420</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>⏳ 實收現金 $209,565 / 已存現金 $191,786 ➔ 待入帳 $17,779</t>
+          <t>⏳ 實收現金 $230,206 / 已存現金 $191,786 ➔ 待入帳 $38,420</t>
         </is>
       </c>
     </row>
@@ -680,20 +680,20 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>303640</v>
+        <v>320710</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>296613</v>
+        <v>313212</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>261323</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>35290</v>
+        <v>51889</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>⏳ 實收LINE Pay $296,613 / 已存 $261,323 ➔ 待入帳 $35,290</t>
+          <t>⏳ 實收LINE Pay $313,212 / 已存 $261,323 ➔ 待入帳 $51,889</t>
         </is>
       </c>
     </row>
@@ -714,20 +714,20 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>64003</v>
+        <v>67408</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>42882</v>
+        <v>45163</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>28996</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>13886</v>
+        <v>16167</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>⏳ 實收Uber Eats $42,882 / 已存 $28,996 ➔ 待入帳 $13,886</t>
+          <t>⏳ 實收Uber Eats $45,163 / 已存 $28,996 ➔ 待入帳 $16,167</t>
         </is>
       </c>
     </row>
@@ -782,20 +782,20 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>384727</v>
+        <v>424705</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>384727</v>
+        <v>424705</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>209228</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>175499</v>
+        <v>215477</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>⏳ 實收現金 $384,727 / 已存現金 $209,228 ➔ 待入帳 $175,499</t>
+          <t>⏳ 實收現金 $424,705 / 已存現金 $209,228 ➔ 待入帳 $215,477</t>
         </is>
       </c>
     </row>
@@ -816,20 +816,20 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>194432</v>
+        <v>215240</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>189933</v>
+        <v>210260</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>93990</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>95943</v>
+        <v>116270</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>⏳ 實收LINE Pay $189,933 / 已存 $93,990 ➔ 待入帳 $95,943</t>
+          <t>⏳ 實收LINE Pay $210,260 / 已存 $93,990 ➔ 待入帳 $116,270</t>
         </is>
       </c>
     </row>
@@ -850,20 +850,20 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>20140</v>
+        <v>20787</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>13890</v>
+        <v>14336</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>5301</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>8589</v>
+        <v>9035</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>⏳ 實收Uber Eats $13,890 / 已存 $5,301 ➔ 待入帳 $8,589</t>
+          <t>⏳ 實收Uber Eats $14,336 / 已存 $5,301 ➔ 待入帳 $9,035</t>
         </is>
       </c>
     </row>
@@ -884,20 +884,20 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>19080</v>
+        <v>21286</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>12669</v>
+        <v>14134</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>12669</v>
+        <v>14134</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>⏳ 實收Foodpanda $12,669 / 已存 $0 ➔ 待入帳 $12,669</t>
+          <t>⏳ 實收Foodpanda $14,134 / 已存 $0 ➔ 待入帳 $14,134</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4139,22 +4139,22 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>❌ 總表U欄空白未填</t>
+          <t>✅ 申報於 2026/10/28 存入 $73,130 (2026-10-21~2026-10-27累計)</t>
         </is>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>⏳ 待存入</t>
+          <t>✓ 金額相符</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>❌ 存摺未見入帳</t>
-        </is>
-      </c>
-      <c r="H10" s="20" t="inlineStr">
-        <is>
-          <t>🔴 門市未存 (留店未存)</t>
+          <t>⏳ 存摺尚未到帳/未更新</t>
+        </is>
+      </c>
+      <c r="H10" s="19" t="inlineStr">
+        <is>
+          <t>🟡 門市已申報 (待銀行入帳)</t>
         </is>
       </c>
       <c r="I10" s="10" t="inlineStr">
@@ -4164,7 +4164,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>門市正常交班處理中，待總表申報或存款</t>
+          <t>總表已登記提存，待存摺更新自動結清 (申報於 2026/10/28 存入 $73,130 (2026-10-21~2026-10-27累計))</t>
         </is>
       </c>
     </row>
@@ -4187,22 +4187,22 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>❌ 總表U欄空白未填</t>
+          <t>✅ 申報於 2026/10/27 存入 $25,361 (2026-10-26~2026-10-28累計)</t>
         </is>
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>⏳ 待存入</t>
+          <t>➕ 溢存 +$780 (應收合 $24,581)</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>❌ 存摺未見入帳</t>
-        </is>
-      </c>
-      <c r="H11" s="20" t="inlineStr">
-        <is>
-          <t>🔴 門市未存 (留店未存)</t>
+          <t>⏳ 存摺尚未到帳/未更新</t>
+        </is>
+      </c>
+      <c r="H11" s="19" t="inlineStr">
+        <is>
+          <t>🟡 門市已申報 (待銀行入帳)</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>門市正常交班處理中，待總表申報或存款</t>
+          <t>【注意短溢：➕ 溢存 +$780 (應收合 $24,581)】總表已登記提存，待存摺更新自動結清 (申報於 2026/10/27 存入 $25,361 (2026-10-26~2026-10-28累計))</t>
         </is>
       </c>
     </row>
@@ -4235,22 +4235,22 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>❌ 總表U欄空白未填</t>
+          <t>✅ 申報於 2026/10/27 存入 $25,361 (2026-10-26~2026-10-28累計)</t>
         </is>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>⏳ 待存入</t>
+          <t>➕ 溢存 +$780 (應收合 $24,581)</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>❌ 存摺未見入帳</t>
-        </is>
-      </c>
-      <c r="H12" s="20" t="inlineStr">
-        <is>
-          <t>🔴 門市未存 (留店未存)</t>
+          <t>⏳ 存摺尚未到帳/未更新</t>
+        </is>
+      </c>
+      <c r="H12" s="19" t="inlineStr">
+        <is>
+          <t>🟡 門市已申報 (待銀行入帳)</t>
         </is>
       </c>
       <c r="I12" s="10" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>門市正常交班處理中，待總表申報或存款</t>
+          <t>【注意短溢：➕ 溢存 +$780 (應收合 $24,581)】總表已登記提存，待存摺更新自動結清 (申報於 2026/10/27 存入 $25,361 (2026-10-26~2026-10-28累計))</t>
         </is>
       </c>
     </row>
@@ -4270,35 +4270,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮 (月下餐飲)</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="D13" s="12" t="n">
-        <v>13890</v>
+        <v>13273</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>❌ 總表U欄空白未填</t>
+          <t>✅ 申報於 2026/10/27 存入 $25,361 (2026-10-26~2026-10-28累計)</t>
         </is>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>⏳ 待存入</t>
+          <t>➕ 溢存 +$780 (應收合 $24,581)</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>❌ 存摺未見入帳</t>
-        </is>
-      </c>
-      <c r="H13" s="20" t="inlineStr">
-        <is>
-          <t>🔴 門市未存 (留店未存)</t>
+          <t>⏳ 存摺尚未到帳/未更新</t>
+        </is>
+      </c>
+      <c r="H13" s="19" t="inlineStr">
+        <is>
+          <t>🟡 門市已申報 (待銀行入帳)</t>
         </is>
       </c>
       <c r="I13" s="10" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>門市正常交班處理中，待總表申報或存款</t>
+          <t>【注意短溢：➕ 溢存 +$780 (應收合 $24,581)】總表已登記提存，待存摺更新自動結清 (申報於 2026/10/27 存入 $25,361 (2026-10-26~2026-10-28累計))</t>
         </is>
       </c>
     </row>
@@ -4318,16 +4318,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>隨意小吃</t>
+          <t>月宮 (月下餐飲)</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="D14" s="12" t="n">
-        <v>18100</v>
+        <v>7368</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -4371,30 +4371,30 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="D15" s="12" t="n">
-        <v>14830</v>
+        <v>13890</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>❌ 總表U欄空白未填</t>
+          <t>✅ 申報於 2026/10/28 存入 $73,130 (2026-10-21~2026-10-27累計)</t>
         </is>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>⏳ 待存入</t>
+          <t>✓ 金額相符</t>
         </is>
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>❌ 存摺未見入帳</t>
-        </is>
-      </c>
-      <c r="H15" s="20" t="inlineStr">
-        <is>
-          <t>🔴 門市未存 (留店未存)</t>
+          <t>⏳ 存摺尚未到帳/未更新</t>
+        </is>
+      </c>
+      <c r="H15" s="19" t="inlineStr">
+        <is>
+          <t>🟡 門市已申報 (待銀行入帳)</t>
         </is>
       </c>
       <c r="I15" s="10" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>門市正常交班處理中，待總表申報或存款</t>
+          <t>總表已登記提存，待存摺更新自動結清 (申報於 2026/10/28 存入 $73,130 (2026-10-21~2026-10-27累計))</t>
         </is>
       </c>
     </row>
@@ -4419,38 +4419,230 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>18100</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>✅ 申報於 2026/10/28 存入 $73,130 (2026-10-21~2026-10-27累計)</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>✓ 金額相符</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>⏳ 存摺尚未到帳/未更新</t>
+        </is>
+      </c>
+      <c r="H16" s="19" t="inlineStr">
+        <is>
+          <t>🟡 門市已申報 (待銀行入帳)</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>0 天</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>總表已登記提存，待存摺更新自動結清 (申報於 2026/10/28 存入 $73,130 (2026-10-21~2026-10-27累計))</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>14830</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>✅ 申報於 2026/10/28 存入 $73,130 (2026-10-21~2026-10-27累計)</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>✓ 金額相符</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>⏳ 存摺尚未到帳/未更新</t>
+        </is>
+      </c>
+      <c r="H17" s="19" t="inlineStr">
+        <is>
+          <t>🟡 門市已申報 (待銀行入帳)</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>0 天</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>總表已登記提存，待存摺更新自動結清 (申報於 2026/10/28 存入 $73,130 (2026-10-21~2026-10-27累計))</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
           <t>2026-10-27</t>
         </is>
       </c>
-      <c r="D16" s="12" t="n">
+      <c r="D18" s="12" t="n">
         <v>15490</v>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>✅ 申報於 2026/10/28 存入 $73,130 (2026-10-21~2026-10-27累計)</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>✓ 金額相符</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>⏳ 存摺尚未到帳/未更新</t>
+        </is>
+      </c>
+      <c r="H18" s="19" t="inlineStr">
+        <is>
+          <t>🟡 門市已申報 (待銀行入帳)</t>
+        </is>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>0 天</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>總表已登記提存，待存摺更新自動結清 (申報於 2026/10/28 存入 $73,130 (2026-10-21~2026-10-27累計))</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>19380</v>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>❌ 總表U欄空白未填</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F19" s="10" t="inlineStr">
         <is>
           <t>⏳ 待存入</t>
         </is>
       </c>
-      <c r="G16" s="10" t="inlineStr">
+      <c r="G19" s="10" t="inlineStr">
         <is>
           <t>❌ 存摺未見入帳</t>
         </is>
       </c>
-      <c r="H16" s="20" t="inlineStr">
+      <c r="H19" s="20" t="inlineStr">
         <is>
           <t>🔴 門市未存 (留店未存)</t>
         </is>
       </c>
-      <c r="I16" s="10" t="inlineStr">
+      <c r="I19" s="10" t="inlineStr">
         <is>
           <t>0 天</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>門市正常交班處理中，待總表申報或存款</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>隨意小吃</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="n">
+        <v>20598</v>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>❌ 總表U欄空白未填</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>⏳ 待存入</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>❌ 存摺未見入帳</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>🔴 門市未存 (留店未存)</t>
+        </is>
+      </c>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>0 天</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>門市正常交班處理中，待總表申報或存款</t>
         </is>
@@ -4556,13 +4748,13 @@
         </is>
       </c>
       <c r="E2" s="12" t="n">
-        <v>303640</v>
+        <v>320710</v>
       </c>
       <c r="F2" s="12" t="n">
-        <v>7027</v>
+        <v>7498</v>
       </c>
       <c r="G2" s="12" t="n">
-        <v>335</v>
+        <v>357</v>
       </c>
       <c r="H2" s="12" t="n">
         <v>0</v>
@@ -4574,7 +4766,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>連加網路 (99024139) 手續費約 $7,027（含可扣抵進項稅額 $335）</t>
+          <t>連加網路 (99024139) 手續費約 $7,498（含可扣抵進項稅額 $357）</t>
         </is>
       </c>
     </row>
@@ -4600,13 +4792,13 @@
         </is>
       </c>
       <c r="E3" s="12" t="n">
-        <v>64003</v>
+        <v>67408</v>
       </c>
       <c r="F3" s="12" t="n">
-        <v>21121</v>
+        <v>22245</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>1006</v>
+        <v>1059</v>
       </c>
       <c r="H3" s="12" t="n">
         <v>0</v>
@@ -4618,7 +4810,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>優步科技 (83118125) 手續費發票約 $21,121（含可扣抵稅額 $1,006）</t>
+          <t>優步科技 (83118125) 手續費發票約 $22,245（含可扣抵稅額 $1,059）</t>
         </is>
       </c>
     </row>
@@ -4644,13 +4836,13 @@
         </is>
       </c>
       <c r="E4" s="12" t="n">
-        <v>194432</v>
+        <v>215240</v>
       </c>
       <c r="F4" s="12" t="n">
-        <v>4499</v>
+        <v>4980</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>214</v>
+        <v>237</v>
       </c>
       <c r="H4" s="12" t="n">
         <v>0</v>
@@ -4662,7 +4854,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>連加網路 (99024139) 手續費約 $4,499（含可扣抵進項稅額 $214）</t>
+          <t>連加網路 (99024139) 手續費約 $4,980（含可扣抵進項稅額 $237）</t>
         </is>
       </c>
     </row>
@@ -4688,13 +4880,13 @@
         </is>
       </c>
       <c r="E5" s="12" t="n">
-        <v>20140</v>
+        <v>20787</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>6250</v>
+        <v>6451</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="H5" s="12" t="n">
         <v>0</v>
@@ -4706,7 +4898,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>優步科技 (83118125) 手續費發票約 $6,250（含可扣抵稅額 $298）</t>
+          <t>優步科技 (83118125) 手續費發票約 $6,451（含可扣抵稅額 $307）</t>
         </is>
       </c>
     </row>
@@ -4732,13 +4924,13 @@
         </is>
       </c>
       <c r="E6" s="12" t="n">
-        <v>19080</v>
+        <v>21286</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>6411</v>
+        <v>7152</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>305</v>
+        <v>341</v>
       </c>
       <c r="H6" s="12" t="n">
         <v>0</v>
@@ -4750,7 +4942,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>富胖達 (53075607) 手續費發票約 $6,411（含可扣抵稅額 $305）</t>
+          <t>富胖達 (53075607) 手續費發票約 $7,152（含可扣抵稅額 $341）</t>
         </is>
       </c>
     </row>
